--- a/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -88,7 +88,10 @@
     <t>CARRERA</t>
   </si>
   <si>
-    <t>PERALTA</t>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>ATLAHUA</t>
@@ -103,7 +106,10 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>RUIZ</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>TEMOXTLE</t>
@@ -112,7 +118,7 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>JOSE</t>
   </si>
   <si>
     <t>CORONA</t>
@@ -121,13 +127,19 @@
     <t>ANA KAREN</t>
   </si>
   <si>
-    <t>JARED ABRAHAM</t>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>AILYN</t>
   </si>
   <si>
     <t>GERMAN</t>
   </si>
   <si>
     <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
   </si>
   <si>
     <t>JONATHAN MOISES</t>
@@ -557,22 +569,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>26</v>
       </c>
       <c r="G3">
-        <v>83.87</v>
+        <v>86.67</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -609,7 +621,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5">
         <v>9</v>
@@ -618,10 +630,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>78.05</v>
+        <v>77.5</v>
       </c>
       <c r="H5">
         <v>6.9</v>
@@ -749,13 +761,13 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -795,13 +807,13 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -929,22 +941,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>26</v>
       </c>
       <c r="G3">
-        <v>83.87</v>
+        <v>86.67</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -981,7 +993,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5">
         <v>9</v>
@@ -990,10 +1002,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>78.05</v>
+        <v>77.5</v>
       </c>
       <c r="H5">
         <v>6.9</v>
@@ -1058,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1096,10 +1108,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1113,22 +1125,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920044</v>
+        <v>22330051920236</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1136,22 +1148,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920261</v>
+        <v>22330051920366</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1159,16 +1171,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920402</v>
+        <v>22330051920261</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1182,47 +1194,93 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920342</v>
+        <v>22330051920402</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
+        <v>22330051920279</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920342</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
         <v>21330051920353</v>
       </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
         <v>9</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F9" t="s">
         <v>14</v>
       </c>
-      <c r="G7">
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -85,27 +85,24 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ATLAHUA</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ATLAHUA</t>
-  </si>
-  <si>
     <t>HUERTA</t>
   </si>
   <si>
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
   </si>
   <si>
     <t>CORONA</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
   </si>
   <si>
     <t>KEVIN ALEXIS</t>
@@ -1070,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1102,7 +1096,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920007</v>
+        <v>22330051920236</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -1111,13 +1105,13 @@
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1125,7 +1119,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920236</v>
+        <v>22330051920366</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1134,7 +1128,7 @@
         <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1148,7 +1142,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920366</v>
+        <v>22330051920261</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1157,13 +1151,13 @@
         <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1171,7 +1165,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920261</v>
+        <v>22330051920402</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1180,7 +1174,7 @@
         <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1194,16 +1188,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920402</v>
+        <v>22330051920279</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1217,39 +1211,39 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920279</v>
+        <v>21330051920342</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920342</v>
+        <v>21330051920353</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1258,29 +1252,6 @@
         <v>14</v>
       </c>
       <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920353</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -85,9 +85,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -103,9 +100,6 @@
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -119,9 +113,6 @@
   </si>
   <si>
     <t>CORONA</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
   </si>
   <si>
     <t>AILYN</t>
@@ -1064,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1096,16 +1087,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920236</v>
+        <v>22330051920366</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1119,22 +1110,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920366</v>
+        <v>22330051920261</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1142,16 +1133,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920261</v>
+        <v>22330051920402</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1165,16 +1156,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920402</v>
+        <v>22330051920279</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1188,39 +1179,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920279</v>
+        <v>21330051920342</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920342</v>
+        <v>21330051920353</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1229,29 +1220,6 @@
         <v>14</v>
       </c>
       <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920353</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -94,12 +97,18 @@
     <t>CARRERA</t>
   </si>
   <si>
-    <t>HUERTA</t>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>VILLEGAS</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -112,9 +121,18 @@
     <t>JOSE</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>CORONA</t>
   </si>
   <si>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
     <t>AILYN</t>
   </si>
   <si>
@@ -127,7 +145,10 @@
     <t>HECTOR MISAEL</t>
   </si>
   <si>
-    <t>JONATHAN MOISES</t>
+    <t>ANGEL DIEGO</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
   </si>
   <si>
     <t>ABIGAIL</t>
@@ -726,16 +747,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>88.23999999999999</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -795,16 +819,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>6.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -818,16 +845,19 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>96.3</v>
+      </c>
+      <c r="H6">
+        <v>7.3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -841,16 +871,19 @@
         <v>44</v>
       </c>
       <c r="D7">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>86.36</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -906,16 +939,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1010,13 +1043,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H6">
         <v>7.3</v>
@@ -1036,16 +1069,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G7">
-        <v>93.18000000000001</v>
+        <v>86.36</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1055,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1087,22 +1120,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920366</v>
+        <v>22330051920021</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1110,22 +1143,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920261</v>
+        <v>22330051920366</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1133,16 +1166,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920402</v>
+        <v>22330051920261</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1156,16 +1189,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920279</v>
+        <v>22330051920402</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1179,47 +1212,93 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920342</v>
+        <v>22330051920279</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920353</v>
+        <v>21330051920308</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920323</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920353</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
         <v>14</v>
       </c>
-      <c r="G7">
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,9 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>MOTA</t>
   </si>
   <si>
@@ -109,15 +112,15 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
     <t>JOSE</t>
   </si>
   <si>
@@ -140,6 +143,9 @@
   </si>
   <si>
     <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
   </si>
   <si>
     <t>HECTOR MISAEL</t>
@@ -773,16 +779,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -796,16 +805,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>78.05</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -819,19 +831,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -965,16 +977,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>86.67</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -991,13 +1003,13 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>80.48999999999999</v>
+        <v>78.05</v>
       </c>
       <c r="H4">
         <v>6.6</v>
@@ -1017,16 +1029,16 @@
         <v>9</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>77.5</v>
+        <v>75</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1088,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1126,10 +1138,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1149,10 +1161,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1175,7 +1187,7 @@
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1198,7 +1210,7 @@
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1212,16 +1224,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920279</v>
+        <v>22330051920404</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1235,22 +1247,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920308</v>
+        <v>22330051920279</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1258,7 +1270,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920323</v>
+        <v>21330051920308</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1267,7 +1279,7 @@
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1281,7 +1293,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920353</v>
+        <v>21330051920323</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
@@ -1290,15 +1302,38 @@
         <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920353</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
         <v>14</v>
       </c>
-      <c r="G9">
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -91,45 +91,39 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>ATLAHUA</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>VILLEGAS</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SEGURA</t>
   </si>
   <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>CORONA</t>
   </si>
   <si>
@@ -139,22 +133,19 @@
     <t>AILYN</t>
   </si>
   <si>
-    <t>GERMAN</t>
-  </si>
-  <si>
     <t>GUILLERMO SAUL</t>
   </si>
   <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>ANGEL DIEGO</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
     <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
-    <t>ANGEL DIEGO</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
   </si>
   <si>
     <t>ABIGAIL</t>
@@ -1100,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1138,10 +1129,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1161,10 +1152,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1178,16 +1169,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920261</v>
+        <v>22330051920402</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1201,16 +1192,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920402</v>
+        <v>22330051920279</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1224,22 +1215,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920404</v>
+        <v>21330051920308</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1247,22 +1238,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920279</v>
+        <v>21330051920323</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1270,70 +1261,47 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920308</v>
+        <v>22330051920404</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920323</v>
+        <v>21330051920353</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920353</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -91,9 +91,6 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>MOTA</t>
   </si>
   <si>
@@ -109,9 +106,6 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>JOSE</t>
   </si>
   <si>
@@ -131,9 +125,6 @@
   </si>
   <si>
     <t>AILYN</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAUL</t>
   </si>
   <si>
     <t>HECTOR MISAEL</t>
@@ -601,10 +592,10 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>33</v>
@@ -613,7 +604,7 @@
         <v>80.48999999999999</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -627,19 +618,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>77.5</v>
+        <v>80</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -796,19 +787,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>78.05</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -822,19 +813,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -991,16 +982,16 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>78.05</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H4">
         <v>6.6</v>
@@ -1017,19 +1008,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1091,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1129,10 +1120,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1152,10 +1143,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1169,16 +1160,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920402</v>
+        <v>22330051920279</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1192,22 +1183,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920279</v>
+        <v>21330051920308</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1215,16 +1206,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920308</v>
+        <v>21330051920323</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1238,70 +1229,47 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920323</v>
+        <v>22330051920404</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920404</v>
+        <v>21330051920353</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920353</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,9 @@
     <t>MEJIA</t>
   </si>
   <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -106,6 +109,9 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>JOSE</t>
   </si>
   <si>
@@ -122,6 +128,9 @@
   </si>
   <si>
     <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>CRHIS AMINADAB</t>
   </si>
   <si>
     <t>AILYN</t>
@@ -1082,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1120,10 +1129,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1137,16 +1146,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920366</v>
+        <v>22330051920239</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1160,22 +1169,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920279</v>
+        <v>22330051920366</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1183,22 +1192,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920308</v>
+        <v>22330051920279</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1206,16 +1215,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920323</v>
+        <v>21330051920308</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1229,47 +1238,70 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920404</v>
+        <v>21330051920323</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920353</v>
+        <v>22330051920404</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920353</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
         <v>9</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F9" t="s">
         <v>14</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -85,51 +85,30 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
     <t>GAMBOA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>MOTA</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
     <t>JOSE</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>SEGURA</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
-  </si>
-  <si>
     <t>CRHIS AMINADAB</t>
   </si>
   <si>
@@ -139,16 +118,10 @@
     <t>HECTOR MISAEL</t>
   </si>
   <si>
-    <t>ANGEL DIEGO</t>
-  </si>
-  <si>
     <t>DIEGO EMILIO</t>
   </si>
   <si>
     <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
   </si>
 </sst>
 </file>
@@ -942,13 +915,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H2">
         <v>7.3</v>
@@ -968,16 +941,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>90</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1046,16 +1019,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1091,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1123,22 +1096,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920021</v>
+        <v>22330051920239</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1146,16 +1119,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920239</v>
+        <v>22330051920366</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1169,22 +1142,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920366</v>
+        <v>22330051920279</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1192,22 +1165,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920279</v>
+        <v>21330051920323</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1215,93 +1188,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920308</v>
+        <v>22330051920404</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920323</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920404</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920353</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -88,40 +88,19 @@
     <t>GAMBOA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>JOSE</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
     <t>CRHIS AMINADAB</t>
   </si>
   <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
     <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
   </si>
 </sst>
 </file>
@@ -967,13 +946,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>82.93000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="H4">
         <v>6.6</v>
@@ -993,16 +972,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1064,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1102,10 +1081,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
         <v>26</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1119,7 +1098,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920366</v>
+        <v>21330051920323</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1128,85 +1107,16 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920279</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920323</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920404</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
@@ -85,22 +85,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>GAMBOA</t>
   </si>
   <si>
-    <t>ROMERO</t>
+    <t>ALVAREZ</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>MONSERRAT</t>
   </si>
   <si>
     <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
   </si>
 </sst>
 </file>
@@ -1024,16 +1024,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7">
-        <v>86.36</v>
+        <v>88.64</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920239</v>
+        <v>22330051920281</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -1090,7 +1090,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920323</v>
+        <v>22330051920239</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1110,13 +1110,13 @@
         <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -85,16 +85,34 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
     <t>GAMBOA</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
     <t>APALE</t>
+  </si>
+  <si>
+    <t>JARED ABRAHAM</t>
+  </si>
+  <si>
+    <t>FERNANDA MARGARITA</t>
   </si>
   <si>
     <t>MONSERRAT</t>
@@ -1043,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1075,22 +1093,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920281</v>
+        <v>22330051920044</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1098,16 +1116,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920239</v>
+        <v>22330051920233</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1116,6 +1134,52 @@
         <v>12</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920281</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920239</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>
